--- a/03_Output/Descriptives/Table_descriptives.xlsx
+++ b/03_Output/Descriptives/Table_descriptives.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/jdconejeros_uc_cl/Documents/Research/Pollution_PerinatalOutcomes_Temuco26/03_Output/Descriptives/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_0CB245461643F8D266075C52F37BD2725A4121CF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0C413A6-BED8-7D41-B0CF-8E53F2FEF2D3}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_26EF255A1643F8D266075C52F37BD2727A44A500" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABBAA7F6-AFF5-A748-AA70-A65A4BEF71AF}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="-28800" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptives" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="339">
   <si>
     <t>Variable</t>
   </si>
@@ -28,28 +28,28 @@
     <t>Characteristic</t>
   </si>
   <si>
-    <t>All.sample</t>
-  </si>
-  <si>
-    <t>Preterm.birth</t>
-  </si>
-  <si>
-    <t>Very.preterm.birth</t>
-  </si>
-  <si>
-    <t>Moderately.preterm.birth</t>
-  </si>
-  <si>
-    <t>Late.preterm.birth</t>
-  </si>
-  <si>
-    <t>Low.birth.weight</t>
-  </si>
-  <si>
-    <t>Very.low.birth.weight</t>
-  </si>
-  <si>
-    <t>Small.for.gestational.age</t>
+    <t>All sample</t>
+  </si>
+  <si>
+    <t>Preterm birth</t>
+  </si>
+  <si>
+    <t>Very preterm birth</t>
+  </si>
+  <si>
+    <t>Moderately preterm birth</t>
+  </si>
+  <si>
+    <t>Late preterm birth</t>
+  </si>
+  <si>
+    <t>Low birth weight</t>
+  </si>
+  <si>
+    <t>Very low birth weight</t>
+  </si>
+  <si>
+    <t>Small for gestational age</t>
   </si>
   <si>
     <t>N</t>
@@ -136,6 +136,27 @@
     <t>26.2 (SD=7.1)</t>
   </si>
   <si>
+    <t>para</t>
+  </si>
+  <si>
+    <t>0.9 (SD=1.1)</t>
+  </si>
+  <si>
+    <t>0.8 (SD=1.1)</t>
+  </si>
+  <si>
+    <t>0.8 (SD=0.9)</t>
+  </si>
+  <si>
+    <t>0.7 (SD=0.9)</t>
+  </si>
+  <si>
+    <t>0.8 (SD=1.0)</t>
+  </si>
+  <si>
+    <t>0.7 (SD=1.0)</t>
+  </si>
+  <si>
     <t>sexo_rn</t>
   </si>
   <si>
@@ -217,6 +238,372 @@
     <t>56.9% (n=887)</t>
   </si>
   <si>
+    <t>education</t>
+  </si>
+  <si>
+    <t>Higher</t>
+  </si>
+  <si>
+    <t>20.5% (n=3163)</t>
+  </si>
+  <si>
+    <t>30.3% (n=402)</t>
+  </si>
+  <si>
+    <t>30.7% (n=59)</t>
+  </si>
+  <si>
+    <t>43.0% (n=43)</t>
+  </si>
+  <si>
+    <t>28.2% (n=263)</t>
+  </si>
+  <si>
+    <t>29.8% (n=307)</t>
+  </si>
+  <si>
+    <t>23.4% (n=66)</t>
+  </si>
+  <si>
+    <t>21.9% (n=342)</t>
+  </si>
+  <si>
+    <t>None or primary</t>
+  </si>
+  <si>
+    <t>13.2% (n=2029)</t>
+  </si>
+  <si>
+    <t>10.7% (n=142)</t>
+  </si>
+  <si>
+    <t>9.4% (n=18)</t>
+  </si>
+  <si>
+    <t>11.0% (n=11)</t>
+  </si>
+  <si>
+    <t>11.3% (n=106)</t>
+  </si>
+  <si>
+    <t>11.1% (n=114)</t>
+  </si>
+  <si>
+    <t>13.5% (n=38)</t>
+  </si>
+  <si>
+    <t>12.3% (n=192)</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>66.1% (n=10178)</t>
+  </si>
+  <si>
+    <t>58.7% (n=779)</t>
+  </si>
+  <si>
+    <t>59.4% (n=114)</t>
+  </si>
+  <si>
+    <t>46.0% (n=46)</t>
+  </si>
+  <si>
+    <t>60.3% (n=563)</t>
+  </si>
+  <si>
+    <t>58.8% (n=606)</t>
+  </si>
+  <si>
+    <t>62.4% (n=176)</t>
+  </si>
+  <si>
+    <t>65.5% (n=1022)</t>
+  </si>
+  <si>
+    <t>health_insurance</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>2.1% (n=317)</t>
+  </si>
+  <si>
+    <t>2.5% (n=33)</t>
+  </si>
+  <si>
+    <t>4.7% (n=9)</t>
+  </si>
+  <si>
+    <t>3.0% (n=3)</t>
+  </si>
+  <si>
+    <t>1.7% (n=16)</t>
+  </si>
+  <si>
+    <t>2.4% (n=25)</t>
+  </si>
+  <si>
+    <t>2.1% (n=6)</t>
+  </si>
+  <si>
+    <t>2.6% (n=40)</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>97.9% (n=15081)</t>
+  </si>
+  <si>
+    <t>97.5% (n=1293)</t>
+  </si>
+  <si>
+    <t>95.3% (n=183)</t>
+  </si>
+  <si>
+    <t>97.0% (n=97)</t>
+  </si>
+  <si>
+    <t>98.3% (n=918)</t>
+  </si>
+  <si>
+    <t>97.6% (n=1006)</t>
+  </si>
+  <si>
+    <t>97.9% (n=276)</t>
+  </si>
+  <si>
+    <t>97.4% (n=1520)</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>Employed</t>
+  </si>
+  <si>
+    <t>30.1% (n=4642)</t>
+  </si>
+  <si>
+    <t>41.2% (n=546)</t>
+  </si>
+  <si>
+    <t>47.9% (n=92)</t>
+  </si>
+  <si>
+    <t>39.0% (n=39)</t>
+  </si>
+  <si>
+    <t>39.6% (n=370)</t>
+  </si>
+  <si>
+    <t>38.8% (n=400)</t>
+  </si>
+  <si>
+    <t>30.1% (n=85)</t>
+  </si>
+  <si>
+    <t>29.9% (n=467)</t>
+  </si>
+  <si>
+    <t>Unemployed</t>
+  </si>
+  <si>
+    <t>68.6% (n=10568)</t>
+  </si>
+  <si>
+    <t>56.6% (n=751)</t>
+  </si>
+  <si>
+    <t>49.5% (n=95)</t>
+  </si>
+  <si>
+    <t>58.0% (n=58)</t>
+  </si>
+  <si>
+    <t>59.1% (n=552)</t>
+  </si>
+  <si>
+    <t>58.3% (n=601)</t>
+  </si>
+  <si>
+    <t>67.0% (n=189)</t>
+  </si>
+  <si>
+    <t>68.4% (n=1067)</t>
+  </si>
+  <si>
+    <t>first_birth</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>53.5% (n=8239)</t>
+  </si>
+  <si>
+    <t>49.8% (n=660)</t>
+  </si>
+  <si>
+    <t>48.0% (n=48)</t>
+  </si>
+  <si>
+    <t>50.4% (n=471)</t>
+  </si>
+  <si>
+    <t>47.1% (n=486)</t>
+  </si>
+  <si>
+    <t>44.3% (n=125)</t>
+  </si>
+  <si>
+    <t>41.3% (n=644)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>46.5% (n=7159)</t>
+  </si>
+  <si>
+    <t>50.2% (n=666)</t>
+  </si>
+  <si>
+    <t>50.5% (n=97)</t>
+  </si>
+  <si>
+    <t>52.0% (n=52)</t>
+  </si>
+  <si>
+    <t>49.6% (n=463)</t>
+  </si>
+  <si>
+    <t>52.9% (n=545)</t>
+  </si>
+  <si>
+    <t>55.7% (n=157)</t>
+  </si>
+  <si>
+    <t>58.7% (n=916)</t>
+  </si>
+  <si>
+    <t>cesarea</t>
+  </si>
+  <si>
+    <t>Cesarean</t>
+  </si>
+  <si>
+    <t>34.7% (n=5340)</t>
+  </si>
+  <si>
+    <t>55.8% (n=740)</t>
+  </si>
+  <si>
+    <t>62.5% (n=120)</t>
+  </si>
+  <si>
+    <t>65.0% (n=65)</t>
+  </si>
+  <si>
+    <t>53.1% (n=496)</t>
+  </si>
+  <si>
+    <t>61.3% (n=632)</t>
+  </si>
+  <si>
+    <t>53.9% (n=152)</t>
+  </si>
+  <si>
+    <t>40.6% (n=634)</t>
+  </si>
+  <si>
+    <t>Spontaneous</t>
+  </si>
+  <si>
+    <t>65.3% (n=10058)</t>
+  </si>
+  <si>
+    <t>44.2% (n=586)</t>
+  </si>
+  <si>
+    <t>37.5% (n=72)</t>
+  </si>
+  <si>
+    <t>35.0% (n=35)</t>
+  </si>
+  <si>
+    <t>46.9% (n=438)</t>
+  </si>
+  <si>
+    <t>38.7% (n=399)</t>
+  </si>
+  <si>
+    <t>46.1% (n=130)</t>
+  </si>
+  <si>
+    <t>59.4% (n=926)</t>
+  </si>
+  <si>
+    <t>comuna</t>
+  </si>
+  <si>
+    <t>PLC</t>
+  </si>
+  <si>
+    <t>17.3% (n=2661)</t>
+  </si>
+  <si>
+    <t>14.8% (n=196)</t>
+  </si>
+  <si>
+    <t>14.6% (n=28)</t>
+  </si>
+  <si>
+    <t>10.0% (n=10)</t>
+  </si>
+  <si>
+    <t>15.8% (n=148)</t>
+  </si>
+  <si>
+    <t>14.5% (n=150)</t>
+  </si>
+  <si>
+    <t>17.7% (n=50)</t>
+  </si>
+  <si>
+    <t>16.0% (n=250)</t>
+  </si>
+  <si>
+    <t>TEM</t>
+  </si>
+  <si>
+    <t>82.7% (n=12737)</t>
+  </si>
+  <si>
+    <t>85.2% (n=1130)</t>
+  </si>
+  <si>
+    <t>85.4% (n=164)</t>
+  </si>
+  <si>
+    <t>90.0% (n=90)</t>
+  </si>
+  <si>
+    <t>84.2% (n=786)</t>
+  </si>
+  <si>
+    <t>85.5% (n=881)</t>
+  </si>
+  <si>
+    <t>82.3% (n=232)</t>
+  </si>
+  <si>
+    <t>84.0% (n=1310)</t>
+  </si>
+  <si>
     <t>a_nac</t>
   </si>
   <si>
@@ -256,12 +643,6 @@
     <t>12.0% (n=159)</t>
   </si>
   <si>
-    <t>14.6% (n=28)</t>
-  </si>
-  <si>
-    <t>11.0% (n=11)</t>
-  </si>
-  <si>
     <t>11.6% (n=108)</t>
   </si>
   <si>
@@ -295,9 +676,6 @@
     <t>13.4% (n=138)</t>
   </si>
   <si>
-    <t>13.5% (n=38)</t>
-  </si>
-  <si>
     <t>13.6% (n=212)</t>
   </si>
   <si>
@@ -361,9 +739,6 @@
     <t>15.4% (n=204)</t>
   </si>
   <si>
-    <t>15.8% (n=148)</t>
-  </si>
-  <si>
     <t>14.7% (n=152)</t>
   </si>
   <si>
@@ -424,9 +799,6 @@
     <t>7.5% (n=99)</t>
   </si>
   <si>
-    <t>10.0% (n=10)</t>
-  </si>
-  <si>
     <t>7.0% (n=65)</t>
   </si>
   <si>
@@ -653,9 +1025,6 @@
   </si>
   <si>
     <t>9.7% (n=1489)</t>
-  </si>
-  <si>
-    <t>10.7% (n=142)</t>
   </si>
   <si>
     <t>12.0% (n=23)</t>
@@ -1020,19 +1389,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1165,228 +1534,228 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>49</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>50</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>51</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>52</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>53</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>54</v>
-      </c>
-      <c r="I6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>57</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>58</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>62</v>
       </c>
-      <c r="I7" t="s">
-        <v>63</v>
-      </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>66</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>68</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>69</v>
       </c>
-      <c r="F8" t="s">
+      <c r="I8" t="s">
         <v>70</v>
       </c>
-      <c r="G8" t="s">
+      <c r="J8" t="s">
         <v>71</v>
-      </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
         <v>75</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>77</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>78</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>79</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>80</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>81</v>
-      </c>
-      <c r="I9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
         <v>84</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>85</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>86</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>87</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>88</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>89</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>90</v>
-      </c>
-      <c r="I10" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
         <v>93</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>94</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>95</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>96</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>97</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>98</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>99</v>
-      </c>
-      <c r="I11" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>101</v>
@@ -1418,7 +1787,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
         <v>110</v>
@@ -1430,470 +1799,918 @@
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="I14" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="F15" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="J15" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
         <v>132</v>
       </c>
-      <c r="D16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
-      </c>
       <c r="F16" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I16" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J16" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="G17" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I17" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J17" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F18" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G18" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H18" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I18" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J18" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="F19" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G19" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D20" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G20" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="H20" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I20" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J20" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="I21" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="J21" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="H22" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="I22" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="J22" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E23" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F23" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="I23" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
       <c r="J23" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="F24" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="G24" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="H24" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="I24" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="E25" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="G25" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="H25" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="I25" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="E26" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="G26" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="I26" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="J26" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C27" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="E27" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="G27" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
+        <v>239</v>
+      </c>
+      <c r="I27" t="s">
+        <v>240</v>
+      </c>
+      <c r="J27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" t="s">
+        <v>245</v>
+      </c>
+      <c r="F28" t="s">
+        <v>246</v>
+      </c>
+      <c r="G28" t="s">
+        <v>247</v>
+      </c>
+      <c r="H28" t="s">
+        <v>208</v>
+      </c>
+      <c r="I28" t="s">
+        <v>240</v>
+      </c>
+      <c r="J28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" t="s">
+        <v>249</v>
+      </c>
+      <c r="D29" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" t="s">
         <v>214</v>
       </c>
-      <c r="I27" t="s">
-        <v>215</v>
-      </c>
-      <c r="J27" t="s">
-        <v>195</v>
+      <c r="F29" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" t="s">
+        <v>253</v>
+      </c>
+      <c r="I29" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" t="s">
+        <v>257</v>
+      </c>
+      <c r="D30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" t="s">
+        <v>180</v>
+      </c>
+      <c r="G30" t="s">
+        <v>259</v>
+      </c>
+      <c r="H30" t="s">
+        <v>260</v>
+      </c>
+      <c r="I30" t="s">
+        <v>261</v>
+      </c>
+      <c r="J30" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" t="s">
+        <v>264</v>
+      </c>
+      <c r="D31" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s">
+        <v>246</v>
+      </c>
+      <c r="G31" t="s">
+        <v>267</v>
+      </c>
+      <c r="H31" t="s">
+        <v>268</v>
+      </c>
+      <c r="I31" t="s">
+        <v>269</v>
+      </c>
+      <c r="J31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E32" t="s">
+        <v>274</v>
+      </c>
+      <c r="F32" t="s">
+        <v>275</v>
+      </c>
+      <c r="G32" t="s">
+        <v>276</v>
+      </c>
+      <c r="H32" t="s">
+        <v>277</v>
+      </c>
+      <c r="I32" t="s">
+        <v>278</v>
+      </c>
+      <c r="J32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C33" t="s">
+        <v>281</v>
+      </c>
+      <c r="D33" t="s">
+        <v>282</v>
+      </c>
+      <c r="E33" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" t="s">
+        <v>283</v>
+      </c>
+      <c r="G33" t="s">
+        <v>284</v>
+      </c>
+      <c r="H33" t="s">
+        <v>285</v>
+      </c>
+      <c r="I33" t="s">
+        <v>286</v>
+      </c>
+      <c r="J33" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>255</v>
+      </c>
+      <c r="B34" t="s">
+        <v>288</v>
+      </c>
+      <c r="C34" t="s">
+        <v>289</v>
+      </c>
+      <c r="D34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" t="s">
+        <v>291</v>
+      </c>
+      <c r="G34" t="s">
+        <v>276</v>
+      </c>
+      <c r="H34" t="s">
+        <v>292</v>
+      </c>
+      <c r="I34" t="s">
+        <v>293</v>
+      </c>
+      <c r="J34" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>255</v>
+      </c>
+      <c r="B35" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35" t="s">
+        <v>265</v>
+      </c>
+      <c r="E35" t="s">
+        <v>297</v>
+      </c>
+      <c r="F35" t="s">
+        <v>298</v>
+      </c>
+      <c r="G35" t="s">
+        <v>299</v>
+      </c>
+      <c r="H35" t="s">
+        <v>260</v>
+      </c>
+      <c r="I35" t="s">
+        <v>278</v>
+      </c>
+      <c r="J35" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>255</v>
+      </c>
+      <c r="B36" t="s">
+        <v>301</v>
+      </c>
+      <c r="C36" t="s">
+        <v>302</v>
+      </c>
+      <c r="D36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E36" t="s">
+        <v>304</v>
+      </c>
+      <c r="F36" t="s">
+        <v>199</v>
+      </c>
+      <c r="G36" t="s">
+        <v>305</v>
+      </c>
+      <c r="H36" t="s">
+        <v>277</v>
+      </c>
+      <c r="I36" t="s">
+        <v>306</v>
+      </c>
+      <c r="J36" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>255</v>
+      </c>
+      <c r="B37" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" t="s">
+        <v>302</v>
+      </c>
+      <c r="D37" t="s">
+        <v>309</v>
+      </c>
+      <c r="E37" t="s">
+        <v>310</v>
+      </c>
+      <c r="F37" t="s">
+        <v>298</v>
+      </c>
+      <c r="G37" t="s">
+        <v>276</v>
+      </c>
+      <c r="H37" t="s">
+        <v>311</v>
+      </c>
+      <c r="I37" t="s">
+        <v>278</v>
+      </c>
+      <c r="J37" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" t="s">
+        <v>314</v>
+      </c>
+      <c r="D38" t="s">
+        <v>315</v>
+      </c>
+      <c r="E38" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" t="s">
+        <v>275</v>
+      </c>
+      <c r="G38" t="s">
+        <v>316</v>
+      </c>
+      <c r="H38" t="s">
+        <v>317</v>
+      </c>
+      <c r="I38" t="s">
+        <v>318</v>
+      </c>
+      <c r="J38" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>255</v>
+      </c>
+      <c r="B39" t="s">
+        <v>320</v>
+      </c>
+      <c r="C39" t="s">
+        <v>321</v>
+      </c>
+      <c r="D39" t="s">
+        <v>322</v>
+      </c>
+      <c r="E39" t="s">
+        <v>323</v>
+      </c>
+      <c r="F39" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" t="s">
+        <v>324</v>
+      </c>
+      <c r="H39" t="s">
+        <v>325</v>
+      </c>
+      <c r="I39" t="s">
+        <v>318</v>
+      </c>
+      <c r="J39" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>255</v>
+      </c>
+      <c r="B40" t="s">
+        <v>327</v>
+      </c>
+      <c r="C40" t="s">
+        <v>328</v>
+      </c>
+      <c r="D40" t="s">
+        <v>329</v>
+      </c>
+      <c r="E40" t="s">
+        <v>274</v>
+      </c>
+      <c r="F40" t="s">
+        <v>86</v>
+      </c>
+      <c r="G40" t="s">
+        <v>330</v>
+      </c>
+      <c r="H40" t="s">
+        <v>311</v>
+      </c>
+      <c r="I40" t="s">
+        <v>331</v>
+      </c>
+      <c r="J40" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>255</v>
+      </c>
+      <c r="B41" t="s">
+        <v>333</v>
+      </c>
+      <c r="C41" t="s">
+        <v>334</v>
+      </c>
+      <c r="D41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" t="s">
+        <v>335</v>
+      </c>
+      <c r="F41" t="s">
+        <v>86</v>
+      </c>
+      <c r="G41" t="s">
+        <v>336</v>
+      </c>
+      <c r="H41" t="s">
+        <v>337</v>
+      </c>
+      <c r="I41" t="s">
+        <v>338</v>
+      </c>
+      <c r="J41" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
